--- a/public/exports/29189811.xlsx
+++ b/public/exports/29189811.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896977</t>
+          <t xml:space="preserve">311896978</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M150" t="inlineStr">

--- a/public/exports/29189811.xlsx
+++ b/public/exports/29189811.xlsx
@@ -416,26 +416,26 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 14</t>
+          <t xml:space="preserve">Lerpøtvej 55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">8290907</t>
+          <t xml:space="preserve">5756829</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J6">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -491,26 +491,26 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 55</t>
+          <t xml:space="preserve">Lærkevej 8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6862</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756829</t>
+          <t xml:space="preserve">9212294</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J7">
-        <v>310</v>
+        <v>254</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J8">
@@ -656,11 +656,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J9">
-        <v>254</v>
+        <v>812</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -716,26 +716,26 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lærkevej 8</t>
+          <t xml:space="preserve">Tirpitzvej 1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">6862</t>
+          <t xml:space="preserve">6857</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212294</t>
+          <t xml:space="preserve">7867969</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J10">
-        <v>812</v>
+        <v>508</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -791,26 +791,26 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tirpitzvej 1</t>
+          <t xml:space="preserve">Vestergade 5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6857</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7867969</t>
+          <t xml:space="preserve">5081928</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J11">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -876,16 +876,16 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081928</t>
+          <t xml:space="preserve">5081936</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J12">
-        <v>503</v>
+        <v>267</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -951,16 +951,16 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081936</t>
+          <t xml:space="preserve">5081974</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J13">
-        <v>267</v>
+        <v>2228</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1016,45 +1016,45 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 5</t>
+          <t xml:space="preserve">Vesterled 50A</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6851</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081974</t>
+          <t xml:space="preserve">5094591</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J14">
-        <v>2228</v>
+        <v>1136</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve">200044645</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-01-21</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 50A</t>
+          <t xml:space="preserve">Højgårdsparken 1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">6851</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5094591</t>
+          <t xml:space="preserve">1511503</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J15">
-        <v>1136</v>
+        <v>257</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044645</t>
+          <t xml:space="preserve">200048960</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-21</t>
+          <t xml:space="preserve">2021-05-10</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1166,50 +1166,50 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højgårdsparken 1</t>
+          <t xml:space="preserve">Tirpitzvej 1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6857</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511503</t>
+          <t xml:space="preserve">7867969</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J16">
-        <v>257</v>
+        <v>2870</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">200048960</t>
+          <t xml:space="preserve">311253609</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">FULDENDT P/S</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-05-10</t>
+          <t xml:space="preserve">2027-06-13</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1241,40 +1241,40 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tirpitzvej 1</t>
+          <t xml:space="preserve">Rosenvænget 45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6857</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7867969</t>
+          <t xml:space="preserve">7767753</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J17">
-        <v>2870</v>
+        <v>1565</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253609</t>
+          <t xml:space="preserve">311490959</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">FULDENDT P/S</t>
+          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-13</t>
+          <t xml:space="preserve">2031-01-27</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1316,40 +1316,40 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 45</t>
+          <t xml:space="preserve">Ortenvej 64</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">7767753</t>
+          <t xml:space="preserve">1511445</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J18">
-        <v>1565</v>
+        <v>9958</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311490959</t>
+          <t xml:space="preserve">311523520</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-27</t>
+          <t xml:space="preserve">2031-05-28</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1391,40 +1391,40 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ortenvej 64</t>
+          <t xml:space="preserve">Skovparken 5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511445</t>
+          <t xml:space="preserve">100177775</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J19">
-        <v>9958</v>
+        <v>3020</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311523520</t>
+          <t xml:space="preserve">311547428</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-28</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1466,40 +1466,40 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovparken 5</t>
+          <t xml:space="preserve">Lærkevej 8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6862</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">100177775</t>
+          <t xml:space="preserve">5080884</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J20">
-        <v>3020</v>
+        <v>5683</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547428</t>
+          <t xml:space="preserve">311686380</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+          <t xml:space="preserve">VITA Ingeniører</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2033-06-08</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lærkevej 8</t>
+          <t xml:space="preserve">Lyngparken 1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">6862</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5080884</t>
+          <t xml:space="preserve">319097, 319098</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1560,21 +1560,21 @@
         </is>
       </c>
       <c r="J21">
-        <v>5683</v>
+        <v>3711</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686380</t>
+          <t xml:space="preserve">311711209</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">VITA Ingeniører</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-08</t>
+          <t xml:space="preserve">2033-09-28</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1616,30 +1616,30 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngparken 1</t>
+          <t xml:space="preserve">Møllegårdsvej 9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6862</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">319097, 319098</t>
+          <t xml:space="preserve">5079556</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J22">
-        <v>3711</v>
+        <v>917</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311711209</t>
+          <t xml:space="preserve">311730890</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-28</t>
+          <t xml:space="preserve">2033-12-21</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1691,30 +1691,30 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegårdsvej 9</t>
+          <t xml:space="preserve">Egekrattet 7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6862</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5079556</t>
+          <t xml:space="preserve">100545090</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J23">
-        <v>917</v>
+        <v>989</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730890</t>
+          <t xml:space="preserve">311777304</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-21</t>
+          <t xml:space="preserve">2034-08-09</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egekrattet 7</t>
+          <t xml:space="preserve">Vesterbækvej 31</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1776,30 +1776,30 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">100545090</t>
+          <t xml:space="preserve">7427707</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J24">
-        <v>989</v>
+        <v>2030</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311777304</t>
+          <t xml:space="preserve">311832916</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-09</t>
+          <t xml:space="preserve">2035-05-20</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterbækvej 31</t>
+          <t xml:space="preserve">Bredgade 55</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1851,30 +1851,30 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7427707</t>
+          <t xml:space="preserve">5107640</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J25">
-        <v>2030</v>
+        <v>718</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832916</t>
+          <t xml:space="preserve">311844281</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-20</t>
+          <t xml:space="preserve">2035-07-11</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 55</t>
+          <t xml:space="preserve">Lerpøtvej 50A</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107640</t>
+          <t xml:space="preserve">5755831</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1935,11 +1935,11 @@
         </is>
       </c>
       <c r="J26">
-        <v>718</v>
+        <v>521</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311844281</t>
+          <t xml:space="preserve">311844284</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 50A</t>
+          <t xml:space="preserve">Lerpøtvej 50B</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2006,11 +2006,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J27">
-        <v>521</v>
+        <v>674</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 50B</t>
+          <t xml:space="preserve">Lerpøtvej 50C</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2081,11 +2081,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J28">
-        <v>674</v>
+        <v>709</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2141,30 +2141,30 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 50C</t>
+          <t xml:space="preserve">Storegade 59</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6855</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755831</t>
+          <t xml:space="preserve">7968232</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J29">
-        <v>709</v>
+        <v>612</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311844284</t>
+          <t xml:space="preserve">311844285</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2231,11 +2231,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J30">
-        <v>612</v>
+        <v>1830</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2291,40 +2291,40 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 59</t>
+          <t xml:space="preserve">Sønderalle 7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">6855</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">7968232</t>
+          <t xml:space="preserve">8443476</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J31">
-        <v>1830</v>
+        <v>449</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311844285</t>
+          <t xml:space="preserve">311863487</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-11</t>
+          <t xml:space="preserve">2035-10-22</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderalle 7</t>
+          <t xml:space="preserve">Krovej 11B</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8443476</t>
+          <t xml:space="preserve">8296451</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="J32">
-        <v>449</v>
+        <v>635</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863487</t>
+          <t xml:space="preserve">311869486</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-22</t>
+          <t xml:space="preserve">2035-11-20</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krovej 11B</t>
+          <t xml:space="preserve">Troesmosevej 2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8296451</t>
+          <t xml:space="preserve">9998735</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2460,11 +2460,11 @@
         </is>
       </c>
       <c r="J33">
-        <v>635</v>
+        <v>1403</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869486</t>
+          <t xml:space="preserve">311869806</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-20</t>
+          <t xml:space="preserve">2035-11-24</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2531,11 +2531,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J34">
-        <v>1403</v>
+        <v>3244</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2606,11 +2606,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J35">
-        <v>3244</v>
+        <v>634</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2681,15 +2681,15 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J36">
-        <v>634</v>
+        <v>973</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869806</t>
+          <t xml:space="preserve">311869804</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troesmosevej 2</t>
+          <t xml:space="preserve">Blüchers Alle 9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9998735</t>
+          <t xml:space="preserve">5135329</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2760,11 +2760,11 @@
         </is>
       </c>
       <c r="J37">
-        <v>973</v>
+        <v>494</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869804</t>
+          <t xml:space="preserve">311876778</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-24</t>
+          <t xml:space="preserve">2036-01-15</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2816,30 +2816,30 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blüchers Alle 9</t>
+          <t xml:space="preserve">Fåborgvej 90</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6753</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5135329</t>
+          <t xml:space="preserve">5112164</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J38">
-        <v>494</v>
+        <v>408</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876778</t>
+          <t xml:space="preserve">311876768</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2891,30 +2891,30 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fåborgvej 90</t>
+          <t xml:space="preserve">Skolegade 24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">6753</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5112164</t>
+          <t xml:space="preserve">5081116</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J39">
-        <v>408</v>
+        <v>351</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876768</t>
+          <t xml:space="preserve">311876773</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 24</t>
+          <t xml:space="preserve">Skolegade 25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,20 +2976,20 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081116</t>
+          <t xml:space="preserve">5081191</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J40">
-        <v>351</v>
+        <v>2264</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876773</t>
+          <t xml:space="preserve">311876775</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 25</t>
+          <t xml:space="preserve">Sønderskovvej 107</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081191</t>
+          <t xml:space="preserve">5135329</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3060,11 +3060,11 @@
         </is>
       </c>
       <c r="J41">
-        <v>2264</v>
+        <v>4847</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876775</t>
+          <t xml:space="preserve">311876769</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 107</t>
+          <t xml:space="preserve">Debelvej 23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6753</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5135329</t>
+          <t xml:space="preserve">5112771</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3135,11 +3135,11 @@
         </is>
       </c>
       <c r="J42">
-        <v>4847</v>
+        <v>5820</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876769</t>
+          <t xml:space="preserve">311878341</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-15</t>
+          <t xml:space="preserve">2036-01-23</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3206,11 +3206,11 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J43">
-        <v>5820</v>
+        <v>1100</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debelvej 23</t>
+          <t xml:space="preserve">Debelvej 25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5112771</t>
+          <t xml:space="preserve">100043834</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3285,11 +3285,11 @@
         </is>
       </c>
       <c r="J44">
-        <v>1100</v>
+        <v>620</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878341</t>
+          <t xml:space="preserve">311878336</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3341,30 +3341,30 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debelvej 25</t>
+          <t xml:space="preserve">Søndergade 76</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">6753</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">100043834</t>
+          <t xml:space="preserve">5082503</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J45">
-        <v>620</v>
+        <v>264</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878336</t>
+          <t xml:space="preserve">311878455</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-23</t>
+          <t xml:space="preserve">2036-01-24</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 76</t>
+          <t xml:space="preserve">Falkevej 4A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5082503</t>
+          <t xml:space="preserve">317690, 317691</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3435,11 +3435,11 @@
         </is>
       </c>
       <c r="J46">
-        <v>264</v>
+        <v>1070</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878455</t>
+          <t xml:space="preserve">311878488</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-24</t>
+          <t xml:space="preserve">2036-01-25</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkevej 4A</t>
+          <t xml:space="preserve">Højvangen 4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">317690, 317691</t>
+          <t xml:space="preserve">5078282</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3510,11 +3510,11 @@
         </is>
       </c>
       <c r="J47">
-        <v>1070</v>
+        <v>457</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878488</t>
+          <t xml:space="preserve">311878485</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højvangen 4</t>
+          <t xml:space="preserve">Mælkevejen 1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5078282</t>
+          <t xml:space="preserve">5078139</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3585,11 +3585,11 @@
         </is>
       </c>
       <c r="J48">
-        <v>457</v>
+        <v>1440</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878485</t>
+          <t xml:space="preserve">311878543</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-25</t>
+          <t xml:space="preserve">2036-01-26</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3656,11 +3656,11 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J49">
-        <v>1440</v>
+        <v>554</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3716,30 +3716,30 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mælkevejen 1</t>
+          <t xml:space="preserve">Møllevej 1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5078139</t>
+          <t xml:space="preserve">5113229</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J50">
-        <v>554</v>
+        <v>380</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878543</t>
+          <t xml:space="preserve">311878765</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-26</t>
+          <t xml:space="preserve">2036-01-27</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 1</t>
+          <t xml:space="preserve">Egekrattet 10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5113229</t>
+          <t xml:space="preserve">8165975</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="J51">
-        <v>380</v>
+        <v>451</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878765</t>
+          <t xml:space="preserve">311881488</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-27</t>
+          <t xml:space="preserve">2036-02-11</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egekrattet 10</t>
+          <t xml:space="preserve">Egekrattet 8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8165975</t>
+          <t xml:space="preserve">8165976</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3885,11 +3885,11 @@
         </is>
       </c>
       <c r="J52">
-        <v>451</v>
+        <v>370</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881488</t>
+          <t xml:space="preserve">311881489</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egekrattet 8</t>
+          <t xml:space="preserve">Kærhøgevej 2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8165976</t>
+          <t xml:space="preserve">1809437</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3960,11 +3960,11 @@
         </is>
       </c>
       <c r="J53">
-        <v>370</v>
+        <v>497</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881489</t>
+          <t xml:space="preserve">311881487</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærhøgevej 2</t>
+          <t xml:space="preserve">Skolegade 22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809437</t>
+          <t xml:space="preserve">5081117</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4035,11 +4035,11 @@
         </is>
       </c>
       <c r="J54">
-        <v>497</v>
+        <v>1693</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881487</t>
+          <t xml:space="preserve">311881490</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 22</t>
+          <t xml:space="preserve">Stationsvej 19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081117</t>
+          <t xml:space="preserve">5079228</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4110,11 +4110,11 @@
         </is>
       </c>
       <c r="J55">
-        <v>1693</v>
+        <v>528</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881490</t>
+          <t xml:space="preserve">311881512</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 19</t>
+          <t xml:space="preserve">Thorstrupvej 14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5079228</t>
+          <t xml:space="preserve">5078819</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4185,11 +4185,11 @@
         </is>
       </c>
       <c r="J56">
-        <v>528</v>
+        <v>381</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881512</t>
+          <t xml:space="preserve">311881515</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorstrupvej 14</t>
+          <t xml:space="preserve">Thorstrupvej 16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4256,15 +4256,15 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J57">
-        <v>381</v>
+        <v>296</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881515</t>
+          <t xml:space="preserve">311881519</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorstrupvej 16</t>
+          <t xml:space="preserve">Thorstrupvej 18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,20 +4326,20 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5078819</t>
+          <t xml:space="preserve">5078814</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J58">
-        <v>296</v>
+        <v>3019</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881519</t>
+          <t xml:space="preserve">311881536</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorstrupvej 18</t>
+          <t xml:space="preserve">Grødevej 7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6823</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5078814</t>
+          <t xml:space="preserve">5076159</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="J59">
-        <v>3019</v>
+        <v>423</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881536</t>
+          <t xml:space="preserve">311881912</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-11</t>
+          <t xml:space="preserve">2036-02-13</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,17 +4466,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grødevej 7</t>
+          <t xml:space="preserve">Bredgade 39</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6823</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5076159</t>
+          <t xml:space="preserve">5107083</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4485,11 +4485,11 @@
         </is>
       </c>
       <c r="J60">
-        <v>423</v>
+        <v>3381</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881912</t>
+          <t xml:space="preserve">311883233</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-13</t>
+          <t xml:space="preserve">2036-02-20</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,17 +4541,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 39</t>
+          <t xml:space="preserve">Gartnerpassagen 6</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107083</t>
+          <t xml:space="preserve">5082163</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="J61">
-        <v>3381</v>
+        <v>4305</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883233</t>
+          <t xml:space="preserve">311883263</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gartnerpassagen 6</t>
+          <t xml:space="preserve">Jægumsvej 44</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5082163</t>
+          <t xml:space="preserve">5758115</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,11 +4635,11 @@
         </is>
       </c>
       <c r="J62">
-        <v>4305</v>
+        <v>643</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883263</t>
+          <t xml:space="preserve">311883267</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægumsvej 44</t>
+          <t xml:space="preserve">Kildegårdvej 14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6852</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5758115</t>
+          <t xml:space="preserve">5089317</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>643</v>
+        <v>1744</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883267</t>
+          <t xml:space="preserve">311883204</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegårdvej 14</t>
+          <t xml:space="preserve">Kløvbakken 70</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">6852</t>
+          <t xml:space="preserve">6855</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089317</t>
+          <t xml:space="preserve">8245265</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J64">
-        <v>1744</v>
+        <v>452</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883204</t>
+          <t xml:space="preserve">311883265</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvbakken 70</t>
+          <t xml:space="preserve">Krogen 1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">6855</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8245265</t>
+          <t xml:space="preserve">5755579</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4860,11 +4860,11 @@
         </is>
       </c>
       <c r="J65">
-        <v>452</v>
+        <v>366</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883265</t>
+          <t xml:space="preserve">311883234</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogen 1</t>
+          <t xml:space="preserve">Pramstedvej 10C</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755579</t>
+          <t xml:space="preserve">5755568</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,11 +4935,11 @@
         </is>
       </c>
       <c r="J66">
-        <v>366</v>
+        <v>8223</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883234</t>
+          <t xml:space="preserve">311883211</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pramstedvej 10C</t>
+          <t xml:space="preserve">Pramstedvej 12B</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,20 +5001,20 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755568</t>
+          <t xml:space="preserve">5759376</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J67">
-        <v>8223</v>
+        <v>504</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883211</t>
+          <t xml:space="preserve">311883210</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pramstedvej 12B</t>
+          <t xml:space="preserve">Storegade 57</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,20 +5076,20 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5759376</t>
+          <t xml:space="preserve">5754327</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J68">
-        <v>504</v>
+        <v>1377</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883210</t>
+          <t xml:space="preserve">311883205</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 57</t>
+          <t xml:space="preserve">Vestergade 20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5754327</t>
+          <t xml:space="preserve">5088167</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5160,11 +5160,11 @@
         </is>
       </c>
       <c r="J69">
-        <v>1377</v>
+        <v>3489</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883205</t>
+          <t xml:space="preserve">311883264</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5216,17 +5216,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 20</t>
+          <t xml:space="preserve">Østervang 1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5088167</t>
+          <t xml:space="preserve">5757498</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5235,11 +5235,11 @@
         </is>
       </c>
       <c r="J70">
-        <v>3489</v>
+        <v>502</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883264</t>
+          <t xml:space="preserve">311883232</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 1</t>
+          <t xml:space="preserve">Dalgasvej 35</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5757498</t>
+          <t xml:space="preserve">5754804</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5310,11 +5310,11 @@
         </is>
       </c>
       <c r="J71">
-        <v>502</v>
+        <v>413</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883232</t>
+          <t xml:space="preserve">311888577</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-20</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5381,11 +5381,11 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J72">
-        <v>413</v>
+        <v>374</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalgasvej 35</t>
+          <t xml:space="preserve">Isbjerg Møllevej 69A</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,20 +5451,20 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5754804</t>
+          <t xml:space="preserve">10002269</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J73">
-        <v>374</v>
+        <v>285</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888577</t>
+          <t xml:space="preserve">311888784</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5516,30 +5516,30 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isbjerg Møllevej 69A</t>
+          <t xml:space="preserve">Rosenvænget 31</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">10002269</t>
+          <t xml:space="preserve">7767753</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J74">
-        <v>285</v>
+        <v>335</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888784</t>
+          <t xml:space="preserve">311888779</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5606,11 +5606,11 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J75">
-        <v>335</v>
+        <v>490</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5666,30 +5666,30 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 31</t>
+          <t xml:space="preserve">Skolegade 25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7767753</t>
+          <t xml:space="preserve">5106531</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J76">
-        <v>490</v>
+        <v>419</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888779</t>
+          <t xml:space="preserve">311888764</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5741,30 +5741,30 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 25</t>
+          <t xml:space="preserve">Skolegade 27F</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106531</t>
+          <t xml:space="preserve">100083815</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J77">
-        <v>419</v>
+        <v>985</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888764</t>
+          <t xml:space="preserve">311888580</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 27F</t>
+          <t xml:space="preserve">Svanehøjvej 27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">100083815</t>
+          <t xml:space="preserve">9212270</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,11 +5835,11 @@
         </is>
       </c>
       <c r="J78">
-        <v>985</v>
+        <v>2216</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888580</t>
+          <t xml:space="preserve">311888785</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5891,30 +5891,30 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanehøjvej 27</t>
+          <t xml:space="preserve">Toften 2H</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212270</t>
+          <t xml:space="preserve">5106531</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J79">
-        <v>2216</v>
+        <v>512</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888785</t>
+          <t xml:space="preserve">311888770</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5966,30 +5966,30 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toften 2H</t>
+          <t xml:space="preserve">Vadgårdsvej 17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106531</t>
+          <t xml:space="preserve">5099212</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J80">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888770</t>
+          <t xml:space="preserve">311888780</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vadgårdsvej 17</t>
+          <t xml:space="preserve">Vardevej 1A</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5099212</t>
+          <t xml:space="preserve">5106531</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6060,11 +6060,11 @@
         </is>
       </c>
       <c r="J81">
-        <v>525</v>
+        <v>2544</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888780</t>
+          <t xml:space="preserve">311888776</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 1A</t>
+          <t xml:space="preserve">Vardevej 1B</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6131,15 +6131,15 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J82">
-        <v>2544</v>
+        <v>428</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888776</t>
+          <t xml:space="preserve">311888760</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6191,30 +6191,30 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 1B</t>
+          <t xml:space="preserve">Vestervold 11A</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106531</t>
+          <t xml:space="preserve">5756377</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J83">
-        <v>428</v>
+        <v>1527</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888760</t>
+          <t xml:space="preserve">311888579</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervold 11A</t>
+          <t xml:space="preserve">Vestervold 11C</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756377</t>
+          <t xml:space="preserve">5756447</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6285,11 +6285,11 @@
         </is>
       </c>
       <c r="J84">
-        <v>1527</v>
+        <v>384</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888579</t>
+          <t xml:space="preserve">311888578</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervold 11C</t>
+          <t xml:space="preserve">Abildvej 25</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756447</t>
+          <t xml:space="preserve">1511385</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6360,11 +6360,11 @@
         </is>
       </c>
       <c r="J85">
-        <v>384</v>
+        <v>3442</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888578</t>
+          <t xml:space="preserve">311888935</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-03-20</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6431,11 +6431,11 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J86">
-        <v>3442</v>
+        <v>969</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6506,11 +6506,11 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J87">
-        <v>969</v>
+        <v>1067</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6581,11 +6581,11 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J88">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abildvej 25</t>
+          <t xml:space="preserve">Abildvej 35</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6656,15 +6656,15 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J89">
-        <v>1052</v>
+        <v>1970</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888935</t>
+          <t xml:space="preserve">311888912</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6716,30 +6716,30 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abildvej 35</t>
+          <t xml:space="preserve">Lindealle 8</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511385</t>
+          <t xml:space="preserve">5081802</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J90">
-        <v>1970</v>
+        <v>778</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888912</t>
+          <t xml:space="preserve">311888957</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindealle 8</t>
+          <t xml:space="preserve">Skolegade 11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,20 +6801,20 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081802</t>
+          <t xml:space="preserve">5081139</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J91">
-        <v>778</v>
+        <v>1624</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888957</t>
+          <t xml:space="preserve">311888955</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6881,11 +6881,11 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J92">
-        <v>1624</v>
+        <v>2910</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -6956,11 +6956,11 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J93">
-        <v>2910</v>
+        <v>740</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7031,11 +7031,11 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J94">
-        <v>740</v>
+        <v>460</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7091,30 +7091,30 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 11</t>
+          <t xml:space="preserve">Bytoften 2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081139</t>
+          <t xml:space="preserve">5756643</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J95">
-        <v>460</v>
+        <v>6003</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888955</t>
+          <t xml:space="preserve">311892635</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-20</t>
+          <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 2</t>
+          <t xml:space="preserve">Flyvepladsvej 2B</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,20 +7176,20 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756643</t>
+          <t xml:space="preserve">5107795</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J96">
-        <v>6003</v>
+        <v>265</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892635</t>
+          <t xml:space="preserve">311892714</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flyvepladsvej 2B</t>
+          <t xml:space="preserve">Kirkegade 1B</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7251,20 +7251,20 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107795</t>
+          <t xml:space="preserve">5107190</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J97">
-        <v>265</v>
+        <v>1435</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892714</t>
+          <t xml:space="preserve">311892637</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7316,30 +7316,30 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 1B</t>
+          <t xml:space="preserve">Kirkegade 60</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107190</t>
+          <t xml:space="preserve">9722879</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J98">
-        <v>1435</v>
+        <v>783</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892637</t>
+          <t xml:space="preserve">311892648</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7391,30 +7391,30 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 60</t>
+          <t xml:space="preserve">Krogen 3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722879</t>
+          <t xml:space="preserve">100019865</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J99">
-        <v>783</v>
+        <v>799</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892648</t>
+          <t xml:space="preserve">311892885</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogen 3</t>
+          <t xml:space="preserve">Krogen 5</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7481,15 +7481,15 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J100">
-        <v>799</v>
+        <v>827</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892885</t>
+          <t xml:space="preserve">311892716</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogen 5</t>
+          <t xml:space="preserve">Pramstedvej 6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019865</t>
+          <t xml:space="preserve">5755576</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7560,11 +7560,11 @@
         </is>
       </c>
       <c r="J101">
-        <v>827</v>
+        <v>1289</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892716</t>
+          <t xml:space="preserve">311892803</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7616,30 +7616,30 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pramstedvej 6</t>
+          <t xml:space="preserve">Smedebakken 14</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755576</t>
+          <t xml:space="preserve">5130812</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J102">
-        <v>1289</v>
+        <v>672</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892803</t>
+          <t xml:space="preserve">311892655</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebakken 14</t>
+          <t xml:space="preserve">Smedebakken 16</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7706,15 +7706,15 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J103">
-        <v>672</v>
+        <v>1285</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892655</t>
+          <t xml:space="preserve">311892656</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7781,11 +7781,11 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J104">
-        <v>1285</v>
+        <v>815</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -7856,15 +7856,15 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J105">
-        <v>815</v>
+        <v>402</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892656</t>
+          <t xml:space="preserve">311892652</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7916,30 +7916,30 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebakken 16</t>
+          <t xml:space="preserve">Sønder Allé 18A</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5130812</t>
+          <t xml:space="preserve">5098976</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>402</v>
+        <v>3082</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892652</t>
+          <t xml:space="preserve">311892807</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -8006,11 +8006,11 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J107">
-        <v>3082</v>
+        <v>1082</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J108">
@@ -8156,11 +8156,11 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J109">
-        <v>1082</v>
+        <v>343</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønder Allé 18A</t>
+          <t xml:space="preserve">Sønder Allé 18B</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,20 +8226,20 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5098976</t>
+          <t xml:space="preserve">5098950</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J110">
-        <v>343</v>
+        <v>664</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892807</t>
+          <t xml:space="preserve">311892805</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8306,11 +8306,11 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J111">
-        <v>664</v>
+        <v>1460</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -8366,30 +8366,30 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønder Allé 18B</t>
+          <t xml:space="preserve">Vestergade 27</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5098950</t>
+          <t xml:space="preserve">5087533</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J112">
-        <v>1460</v>
+        <v>293</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892805</t>
+          <t xml:space="preserve">311892646</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 27</t>
+          <t xml:space="preserve">Vestergade 31</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8456,15 +8456,15 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J113">
-        <v>293</v>
+        <v>450</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892646</t>
+          <t xml:space="preserve">311892645</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,30 +8516,30 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 31</t>
+          <t xml:space="preserve">Viaduktvej 25B</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5087533</t>
+          <t xml:space="preserve">5083002</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J114">
-        <v>450</v>
+        <v>505</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892645</t>
+          <t xml:space="preserve">311892650</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8591,17 +8591,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viaduktvej 25B</t>
+          <t xml:space="preserve">Østervang 3A</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5083002</t>
+          <t xml:space="preserve">8257259</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="J115">
-        <v>505</v>
+        <v>1222</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892650</t>
+          <t xml:space="preserve">311892719</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 3A</t>
+          <t xml:space="preserve">Lundvej 135A</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8257259</t>
+          <t xml:space="preserve">1511389</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>1222</v>
+        <v>3433</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892719</t>
+          <t xml:space="preserve">311895818</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-08</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8756,11 +8756,11 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J117">
-        <v>3433</v>
+        <v>1008</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -8831,11 +8831,11 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J118">
-        <v>1008</v>
+        <v>827</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundvej 135A</t>
+          <t xml:space="preserve">Lundvej 135B</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8906,15 +8906,15 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J119">
-        <v>827</v>
+        <v>365</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895818</t>
+          <t xml:space="preserve">311895828</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8981,15 +8981,15 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J120">
-        <v>365</v>
+        <v>859</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895828</t>
+          <t xml:space="preserve">311895826</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundvej 135B</t>
+          <t xml:space="preserve">Abildvej 25</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,20 +9051,20 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511389</t>
+          <t xml:space="preserve">8443476</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J121">
-        <v>859</v>
+        <v>1632</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895826</t>
+          <t xml:space="preserve">311896763</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-04-24</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9131,11 +9131,11 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J122">
-        <v>1632</v>
+        <v>2198</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -9191,30 +9191,30 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abildvej 25</t>
+          <t xml:space="preserve">Byagervej 19</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8443476</t>
+          <t xml:space="preserve">5099692</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J123">
-        <v>2198</v>
+        <v>4785</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896763</t>
+          <t xml:space="preserve">311896775</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 19</t>
+          <t xml:space="preserve">Carolineparken 1A</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5099692</t>
+          <t xml:space="preserve">5757501</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>4785</v>
+        <v>1634</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896775</t>
+          <t xml:space="preserve">311896772</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolineparken 1A</t>
+          <t xml:space="preserve">Carolineparken 1G</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9356,11 +9356,11 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J125">
-        <v>1634</v>
+        <v>567</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -9416,30 +9416,30 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolineparken 1G</t>
+          <t xml:space="preserve">Fåborgvej 151</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6753</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5757501</t>
+          <t xml:space="preserve">5112648</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J126">
-        <v>567</v>
+        <v>2385</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896772</t>
+          <t xml:space="preserve">311896787</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9491,30 +9491,30 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fåborgvej 151</t>
+          <t xml:space="preserve">Kirkegade 1C</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">6753</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5112648</t>
+          <t xml:space="preserve">5107106</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J127">
-        <v>2385</v>
+        <v>390</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896787</t>
+          <t xml:space="preserve">311896773</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9566,30 +9566,30 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 1C</t>
+          <t xml:space="preserve">Møllegården 2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6855</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107106</t>
+          <t xml:space="preserve">5106049</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J128">
-        <v>390</v>
+        <v>996</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896773</t>
+          <t xml:space="preserve">311896762</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9656,11 +9656,11 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J129">
-        <v>996</v>
+        <v>1078</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -9716,30 +9716,30 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegården 2</t>
+          <t xml:space="preserve">Solhøjvej 1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6855</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106049</t>
+          <t xml:space="preserve">5134840</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J130">
-        <v>1078</v>
+        <v>760</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896762</t>
+          <t xml:space="preserve">311896782</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solhøjvej 1</t>
+          <t xml:space="preserve">Stålværksvej 13A</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5134840</t>
+          <t xml:space="preserve">5756440</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>760</v>
+        <v>2835</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896782</t>
+          <t xml:space="preserve">311896789</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stålværksvej 13A</t>
+          <t xml:space="preserve">Sønderskovvej 33A</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,20 +9876,20 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756440</t>
+          <t xml:space="preserve">7277566</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J132">
-        <v>2835</v>
+        <v>431</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896789</t>
+          <t xml:space="preserve">311896786</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 33A</t>
+          <t xml:space="preserve">Sønderskovvej 35A</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,20 +9951,20 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">7277566</t>
+          <t xml:space="preserve">5134840</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J133">
-        <v>431</v>
+        <v>724</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896786</t>
+          <t xml:space="preserve">311896785</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,30 +10016,30 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 35A</t>
+          <t xml:space="preserve">Torvegade 17</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5134840</t>
+          <t xml:space="preserve">8879067</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J134">
-        <v>724</v>
+        <v>537</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896785</t>
+          <t xml:space="preserve">311896774</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10091,30 +10091,30 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 17</t>
+          <t xml:space="preserve">Vinkelvej 16A</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">8879067</t>
+          <t xml:space="preserve">5130859</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J135">
-        <v>537</v>
+        <v>977</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896774</t>
+          <t xml:space="preserve">311896759</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 16A</t>
+          <t xml:space="preserve">Vinkelvej 2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10181,11 +10181,11 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J136">
-        <v>977</v>
+        <v>3842</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -10241,17 +10241,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 2</t>
+          <t xml:space="preserve">Yderikvej 40</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6862</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5130859</t>
+          <t xml:space="preserve">100060726</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -10260,11 +10260,11 @@
         </is>
       </c>
       <c r="J137">
-        <v>3842</v>
+        <v>2426</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896759</t>
+          <t xml:space="preserve">311896788</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,17 +10316,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yderikvej 40</t>
+          <t xml:space="preserve">Østergade 17</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">6862</t>
+          <t xml:space="preserve">6823</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">100060726</t>
+          <t xml:space="preserve">5075750</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -10335,11 +10335,11 @@
         </is>
       </c>
       <c r="J138">
-        <v>2426</v>
+        <v>1157</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896788</t>
+          <t xml:space="preserve">311896790</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10406,11 +10406,11 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J139">
-        <v>1157</v>
+        <v>2462</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J140">
-        <v>2462</v>
+        <v>1302</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10556,11 +10556,11 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J141">
-        <v>1302</v>
+        <v>450</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10616,30 +10616,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 17</t>
+          <t xml:space="preserve">Lyngparken 3</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">6823</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5075750</t>
+          <t xml:space="preserve">5755189</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J142">
-        <v>450</v>
+        <v>1252</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896790</t>
+          <t xml:space="preserve">311896976</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-24</t>
+          <t xml:space="preserve">2036-04-27</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,30 +10691,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngparken 3</t>
+          <t xml:space="preserve">Nybrovej 30</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6851</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755189</t>
+          <t xml:space="preserve">736957, 5094333</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J143">
-        <v>1252</v>
+        <v>351</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896976</t>
+          <t xml:space="preserve">311896971</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 30</t>
+          <t xml:space="preserve">Nybrovej 32</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10781,15 +10781,15 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J144">
-        <v>351</v>
+        <v>1533</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896971</t>
+          <t xml:space="preserve">311896972</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 32</t>
+          <t xml:space="preserve">Nybrovej 34</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,20 +10851,20 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">736957, 5094333</t>
+          <t xml:space="preserve">5094366</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J145">
-        <v>1533</v>
+        <v>441</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896972</t>
+          <t xml:space="preserve">311896973</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 34</t>
+          <t xml:space="preserve">Nybrovej 36A</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10931,15 +10931,15 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J146">
-        <v>441</v>
+        <v>2976</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896973</t>
+          <t xml:space="preserve">311896980</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 36A</t>
+          <t xml:space="preserve">Skolegade 59</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6851</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5094366</t>
+          <t xml:space="preserve">5096151</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>2976</v>
+        <v>933</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896980</t>
+          <t xml:space="preserve">311896982</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11081,11 +11081,11 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J148">
-        <v>933</v>
+        <v>1485</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11141,30 +11141,30 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 59</t>
+          <t xml:space="preserve">Torvet 7</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5096151</t>
+          <t xml:space="preserve">5753906</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J149">
-        <v>1485</v>
+        <v>3584</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896982</t>
+          <t xml:space="preserve">311896977</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,17 +11216,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 7</t>
+          <t xml:space="preserve">Vænget 26A</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5753906</t>
+          <t xml:space="preserve">5106609</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,16 +11235,16 @@
         </is>
       </c>
       <c r="J150">
-        <v>3584</v>
+        <v>1477</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896978</t>
+          <t xml:space="preserve">311896979</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11291,17 +11291,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vænget 26A</t>
+          <t xml:space="preserve">Skolevænget 12</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106609</t>
+          <t xml:space="preserve">8839667</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11310,11 +11310,11 @@
         </is>
       </c>
       <c r="J151">
-        <v>1477</v>
+        <v>650</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896979</t>
+          <t xml:space="preserve">311897259</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-27</t>
+          <t xml:space="preserve">2036-04-28</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11381,15 +11381,15 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J152">
-        <v>650</v>
+        <v>713</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897259</t>
+          <t xml:space="preserve">311897257</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11456,15 +11456,15 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J153">
-        <v>713</v>
+        <v>1368</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897257</t>
+          <t xml:space="preserve">311897256</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J154">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J155">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 12</t>
+          <t xml:space="preserve">Skolevænget 12A</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11681,15 +11681,15 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J156">
-        <v>1368</v>
+        <v>437</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897256</t>
+          <t xml:space="preserve">311897264</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 12A</t>
+          <t xml:space="preserve">Skolevænget 19</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,20 +11751,20 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8839667</t>
+          <t xml:space="preserve">5087702</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J157">
-        <v>437</v>
+        <v>1155</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897264</t>
+          <t xml:space="preserve">311897265</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 19</t>
+          <t xml:space="preserve">Torps Alle 4</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5087702</t>
+          <t xml:space="preserve">5088166</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,11 +11835,11 @@
         </is>
       </c>
       <c r="J158">
-        <v>1155</v>
+        <v>695</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897265</t>
+          <t xml:space="preserve">311897266</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torps Alle 4</t>
+          <t xml:space="preserve">Skolevænget 12</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,20 +11901,20 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5088166</t>
+          <t xml:space="preserve">8839667</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J159">
-        <v>695</v>
+        <v>726</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897266</t>
+          <t xml:space="preserve">311897625</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-28</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11981,11 +11981,11 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J160">
-        <v>726</v>
+        <v>5084</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -12041,30 +12041,30 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 12</t>
+          <t xml:space="preserve">Lerpøtvej 55</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8839667</t>
+          <t xml:space="preserve">5756829</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J161">
-        <v>5084</v>
+        <v>2680</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897625</t>
+          <t xml:space="preserve">311918684</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-29</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12131,15 +12131,15 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J162">
-        <v>2680</v>
+        <v>2277</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918684</t>
+          <t xml:space="preserve">311918683</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12206,15 +12206,15 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J163">
-        <v>2277</v>
+        <v>3746</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918683</t>
+          <t xml:space="preserve">311918682</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12281,11 +12281,11 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J164">
-        <v>3746</v>
+        <v>646</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 55</t>
+          <t xml:space="preserve">Lerpøtvej 55A</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12356,11 +12356,11 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J165">
-        <v>646</v>
+        <v>956</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -12416,40 +12416,40 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 55A</t>
+          <t xml:space="preserve">Jernbanegade 14</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756829</t>
+          <t xml:space="preserve">8290907</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J166">
-        <v>956</v>
+        <v>341</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918682</t>
+          <t xml:space="preserve">311931080</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-10-09</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
